--- a/etf_holdings/2026-09-15_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:26</t>
+          <t>2026-09-15 19:53:55</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,17 +509,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.37%5345</t>
+          <t>-4.3%5115</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:26</t>
+          <t>2026-09-15 19:53:55</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,17 +572,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.55%4560</t>
+          <t>-2.85%4430</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:26</t>
+          <t>2026-09-15 19:53:55</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,17 +635,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-1.24%2380</t>
+          <t>+0.21%2385</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:27</t>
+          <t>2026-09-15 19:53:56</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:27</t>
+          <t>2026-09-15 19:53:56</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0%1620</t>
+          <t>+3.09%1670</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+3.09%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1620</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:27</t>
+          <t>2026-09-15 19:53:56</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,17 +824,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.72%970</t>
+          <t>-1.96%951</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.72%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>951</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:27</t>
+          <t>2026-09-15 19:53:56</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:27</t>
+          <t>2026-09-15 19:53:56</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:27</t>
+          <t>2026-09-15 19:53:56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:27</t>
+          <t>2026-09-15 19:53:56</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,17 +1076,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-1.78%3310</t>
+          <t>-5.89%3115</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>-5.89%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3310</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:27</t>
+          <t>2026-09-15 19:53:56</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:29</t>
+          <t>2026-09-15 19:53:57</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,17 +1202,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0%5620</t>
+          <t>-2.77%5440</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-2.77%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5620</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:29</t>
+          <t>2026-09-15 19:53:57</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.57%261.5</t>
+          <t>-1.72%257</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.57%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>261.5</t>
+          <t>257</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:29</t>
+          <t>2026-09-15 19:53:57</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,17 +1328,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-2.31%1055</t>
+          <t>+2.84%1085</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:29</t>
+          <t>2026-09-15 19:53:57</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1391,17 +1391,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.93%2140</t>
+          <t>-2.8%2080</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:29</t>
+          <t>2026-09-15 19:53:57</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1454,17 +1454,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-5.49%2580</t>
+          <t>-3.85%2625</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-5.49%</t>
+          <t>-3.85%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:29</t>
+          <t>2026-09-15 19:53:57</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1517,17 +1517,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.08%6305</t>
+          <t>-2.7%6135</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:29</t>
+          <t>2026-09-15 19:53:57</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1580,17 +1580,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+4.27%1955</t>
+          <t>+1.28%1980</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+4.27%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">

--- a/etf_holdings/2026-09-15_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:55</t>
+          <t>2026-09-15 21:12:50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:55</t>
+          <t>2026-09-15 21:12:50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:55</t>
+          <t>2026-09-15 21:12:50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:56</t>
+          <t>2026-09-15 21:12:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:56</t>
+          <t>2026-09-15 21:12:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:56</t>
+          <t>2026-09-15 21:12:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:56</t>
+          <t>2026-09-15 21:12:51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:56</t>
+          <t>2026-09-15 21:12:51</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:56</t>
+          <t>2026-09-15 21:12:51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:56</t>
+          <t>2026-09-15 21:12:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:56</t>
+          <t>2026-09-15 21:12:51</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:57</t>
+          <t>2026-09-15 21:12:52</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:57</t>
+          <t>2026-09-15 21:12:52</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:57</t>
+          <t>2026-09-15 21:12:52</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:57</t>
+          <t>2026-09-15 21:12:52</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:57</t>
+          <t>2026-09-15 21:12:52</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:57</t>
+          <t>2026-09-15 21:12:52</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:57</t>
+          <t>2026-09-15 21:12:52</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">

--- a/etf_holdings/2026-09-15_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:50</t>
+          <t>2026-09-15 22:23:07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:50</t>
+          <t>2026-09-15 22:23:07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:50</t>
+          <t>2026-09-15 22:23:07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:51</t>
+          <t>2026-09-15 22:23:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:51</t>
+          <t>2026-09-15 22:23:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:51</t>
+          <t>2026-09-15 22:23:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:51</t>
+          <t>2026-09-15 22:23:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:51</t>
+          <t>2026-09-15 22:23:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:51</t>
+          <t>2026-09-15 22:23:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:51</t>
+          <t>2026-09-15 22:23:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:51</t>
+          <t>2026-09-15 22:23:08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:52</t>
+          <t>2026-09-15 22:23:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:52</t>
+          <t>2026-09-15 22:23:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:52</t>
+          <t>2026-09-15 22:23:10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:52</t>
+          <t>2026-09-15 22:23:10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:52</t>
+          <t>2026-09-15 22:23:10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:52</t>
+          <t>2026-09-15 22:23:10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:52</t>
+          <t>2026-09-15 22:23:10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">

--- a/etf_holdings/2026-09-15_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:07</t>
+          <t>2026-09-15 22:29:02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:07</t>
+          <t>2026-09-15 22:29:02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:07</t>
+          <t>2026-09-15 22:29:02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:08</t>
+          <t>2026-09-15 22:29:13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:08</t>
+          <t>2026-09-15 22:29:13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:08</t>
+          <t>2026-09-15 22:29:13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:08</t>
+          <t>2026-09-15 22:29:13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:08</t>
+          <t>2026-09-15 22:29:13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:08</t>
+          <t>2026-09-15 22:29:13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:08</t>
+          <t>2026-09-15 22:29:13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:08</t>
+          <t>2026-09-15 22:29:13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:10</t>
+          <t>2026-09-15 22:29:25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:10</t>
+          <t>2026-09-15 22:29:25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:10</t>
+          <t>2026-09-15 22:29:25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:10</t>
+          <t>2026-09-15 22:29:25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:10</t>
+          <t>2026-09-15 22:29:25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:10</t>
+          <t>2026-09-15 22:29:25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:10</t>
+          <t>2026-09-15 22:29:25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
